--- a/References/References.xlsx
+++ b/References/References.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Learn\مهندسی مالی\#پایان‌نامه\portfolio-selection-using-ml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\a.nezhadshamsi\Desktop\# Portfolio Selection\portfolio-selection-using-ml\References\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC3DF1B-65E1-4B59-B7F1-4546D3AFAF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FA9304-1104-451C-BEE6-ABBCA8B32EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="853" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articles" sheetId="16" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>عنوان مقاله</t>
   </si>
@@ -99,6 +99,13 @@
   </si>
   <si>
     <t>مهدی خزائی</t>
+  </si>
+  <si>
+    <t>مدل انتخاب سبد سرمایه گذاری مبتنی بر پیشبینی با استفاده از ماشین
+بردار پشتیبان</t>
+  </si>
+  <si>
+    <t>محمدامین منادی</t>
   </si>
 </sst>
 </file>
@@ -112,14 +119,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -127,7 +134,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -135,7 +142,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -149,7 +156,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -554,15 +561,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E3CBBBE-CC25-4F44-8377-214039726488}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="17.58203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.58203125" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="11" width="17.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -585,7 +592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
@@ -594,7 +601,7 @@
       <c r="F2" s="7"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
@@ -603,7 +610,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
@@ -612,7 +619,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
@@ -621,7 +628,7 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
@@ -630,7 +637,7 @@
       <c r="F6" s="7"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
@@ -639,7 +646,7 @@
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
     </row>
-    <row r="8" spans="1:17" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17"/>
@@ -655,7 +662,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
@@ -664,7 +671,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="16"/>
       <c r="C10" s="17"/>
@@ -673,7 +680,7 @@
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
@@ -682,7 +689,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
@@ -691,7 +698,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
@@ -700,7 +707,7 @@
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
@@ -709,7 +716,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
@@ -718,7 +725,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
@@ -727,7 +734,7 @@
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
@@ -736,7 +743,7 @@
       <c r="F17" s="18"/>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
@@ -745,7 +752,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
@@ -754,7 +761,7 @@
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
@@ -763,7 +770,7 @@
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
@@ -772,7 +779,7 @@
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -780,7 +787,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -788,7 +795,7 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -796,7 +803,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -804,7 +811,7 @@
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -812,7 +819,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -820,7 +827,7 @@
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -828,7 +835,7 @@
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -836,7 +843,7 @@
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -844,7 +851,7 @@
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -852,7 +859,7 @@
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -860,7 +867,7 @@
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -868,7 +875,7 @@
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -876,7 +883,7 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -884,7 +891,7 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
@@ -892,7 +899,7 @@
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -909,15 +916,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40B35EA-5CDF-48C3-A3C3-C52403DAC4EA}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="17.58203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.58203125" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="11" width="17.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -940,7 +947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
@@ -949,7 +956,7 @@
       <c r="F2" s="7"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
@@ -958,7 +965,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
@@ -967,7 +974,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
@@ -976,7 +983,7 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
@@ -985,7 +992,7 @@
       <c r="F6" s="7"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
@@ -994,7 +1001,7 @@
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
     </row>
-    <row r="8" spans="1:17" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17"/>
@@ -1010,7 +1017,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
@@ -1019,7 +1026,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="16"/>
       <c r="C10" s="17"/>
@@ -1028,7 +1035,7 @@
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
@@ -1037,7 +1044,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
@@ -1046,7 +1053,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
@@ -1055,7 +1062,7 @@
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
@@ -1064,7 +1071,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
@@ -1073,7 +1080,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
@@ -1082,7 +1089,7 @@
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
@@ -1091,7 +1098,7 @@
       <c r="F17" s="18"/>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
@@ -1100,7 +1107,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
@@ -1109,7 +1116,7 @@
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
@@ -1118,7 +1125,7 @@
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
@@ -1127,7 +1134,7 @@
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -1135,7 +1142,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -1143,7 +1150,7 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -1151,7 +1158,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -1159,7 +1166,7 @@
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -1167,7 +1174,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -1175,7 +1182,7 @@
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -1183,7 +1190,7 @@
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -1191,7 +1198,7 @@
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -1199,7 +1206,7 @@
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -1207,7 +1214,7 @@
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -1215,7 +1222,7 @@
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -1223,7 +1230,7 @@
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -1231,7 +1238,7 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -1239,7 +1246,7 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
@@ -1247,7 +1254,7 @@
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -1263,16 +1270,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D50E89E2-3EF9-4B34-A47E-D8430F32588E}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="17.58203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.58203125" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="11" width="17.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1295,7 +1302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="74" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1314,54 +1321,64 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" ht="92.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="6">
-        <v>1398</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" ht="55.5" x14ac:dyDescent="0.3">
+        <v>1400</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
+      <c r="E4" s="6">
+        <v>1398</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="13"/>
       <c r="C6" s="15"/>
@@ -1370,7 +1387,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="13"/>
       <c r="C7" s="15"/>
@@ -1379,7 +1396,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="13"/>
       <c r="C8" s="15"/>
@@ -1388,7 +1405,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="13"/>
       <c r="C9" s="15"/>
@@ -1397,7 +1414,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="13"/>
       <c r="C10" s="15"/>
@@ -1406,7 +1423,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="13"/>
       <c r="C11" s="15"/>
@@ -1415,9 +1432,18 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{80A17E4B-C196-40CB-9FD4-5D43814FA52D}"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{80A17E4B-C196-40CB-9FD4-5D43814FA52D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
